--- a/artfynd/A 41242-2022 artfynd.xlsx
+++ b/artfynd/A 41242-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125454231</v>
       </c>
       <c r="B2" t="n">
-        <v>105029</v>
+        <v>105205</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 41242-2022 artfynd.xlsx
+++ b/artfynd/A 41242-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125454231</v>
       </c>
       <c r="B2" t="n">
-        <v>105260</v>
+        <v>105267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41242-2022 artfynd.xlsx
+++ b/artfynd/A 41242-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125454231</v>
       </c>
       <c r="B2" t="n">
-        <v>105267</v>
+        <v>105270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41242-2022 artfynd.xlsx
+++ b/artfynd/A 41242-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125454231</v>
       </c>
       <c r="B2" t="n">
-        <v>105270</v>
+        <v>105274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41242-2022 artfynd.xlsx
+++ b/artfynd/A 41242-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125454231</v>
       </c>
       <c r="B2" t="n">
-        <v>105274</v>
+        <v>105275</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41242-2022 artfynd.xlsx
+++ b/artfynd/A 41242-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125454231</v>
       </c>
       <c r="B2" t="n">
-        <v>105275</v>
+        <v>105277</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
